--- a/pib_nowcast/data/last_data_at_time.xlsx
+++ b/pib_nowcast/data/last_data_at_time.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>cons_energ_indusrial</t>
+          <t>cons_energ_industrial</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -28160,1210 +28160,968 @@
       <c r="A2" s="1" t="n">
         <v>35125</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>96.84</t>
-        </is>
+      <c r="B2" t="n">
+        <v>96.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>35217</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>100.12</t>
-        </is>
+      <c r="B3" t="n">
+        <v>100.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>35309</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>107.56</t>
-        </is>
+      <c r="B4" t="n">
+        <v>107.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>35400</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>104.31</t>
-        </is>
+      <c r="B5" t="n">
+        <v>104.31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
         <v>35490</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100.13</t>
-        </is>
+      <c r="B6" t="n">
+        <v>100.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
         <v>35582</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>104.88</t>
-        </is>
+      <c r="B7" t="n">
+        <v>104.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
         <v>35674</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>109.49</t>
-        </is>
+      <c r="B8" t="n">
+        <v>109.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
         <v>35765</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>108.21</t>
-        </is>
+      <c r="B9" t="n">
+        <v>108.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>35855</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>101.14</t>
-        </is>
+      <c r="B10" t="n">
+        <v>101.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
         <v>35947</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>106.46</t>
-        </is>
+      <c r="B11" t="n">
+        <v>106.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
         <v>36039</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>109.88</t>
-        </is>
+      <c r="B12" t="n">
+        <v>109.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
         <v>36130</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>106.66</t>
-        </is>
+      <c r="B13" t="n">
+        <v>106.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>36220</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>101.92</t>
-        </is>
+      <c r="B14" t="n">
+        <v>101.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>36312</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>106.04</t>
-        </is>
+      <c r="B15" t="n">
+        <v>106.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
         <v>36404</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>109.20</t>
-        </is>
+      <c r="B16" t="n">
+        <v>109.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>36495</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>108.97</t>
-        </is>
+      <c r="B17" t="n">
+        <v>108.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
         <v>36586</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>106.40</t>
-        </is>
+      <c r="B18" t="n">
+        <v>106.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>36678</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>110.25</t>
-        </is>
+      <c r="B19" t="n">
+        <v>110.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>36770</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>114.19</t>
-        </is>
+      <c r="B20" t="n">
+        <v>114.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
         <v>36861</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>113.98</t>
-        </is>
+      <c r="B21" t="n">
+        <v>113.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
         <v>36951</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>110.10</t>
-        </is>
+      <c r="B22" t="n">
+        <v>110.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
         <v>37043</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>112.82</t>
-        </is>
+      <c r="B23" t="n">
+        <v>112.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
         <v>37135</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>114.71</t>
-        </is>
+      <c r="B24" t="n">
+        <v>114.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>37226</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>113.38</t>
-        </is>
+      <c r="B25" t="n">
+        <v>113.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
         <v>37316</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>110.63</t>
-        </is>
+      <c r="B26" t="n">
+        <v>110.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
         <v>37408</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>115.41</t>
-        </is>
+      <c r="B27" t="n">
+        <v>115.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
         <v>37500</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>119.50</t>
-        </is>
+      <c r="B28" t="n">
+        <v>119.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
         <v>37591</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>119.24</t>
-        </is>
+      <c r="B29" t="n">
+        <v>119.24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
         <v>37681</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>113.58</t>
-        </is>
+      <c r="B30" t="n">
+        <v>113.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
         <v>37773</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>116.31</t>
-        </is>
+      <c r="B31" t="n">
+        <v>116.31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
         <v>37865</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>120.25</t>
-        </is>
+      <c r="B32" t="n">
+        <v>120.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
         <v>37956</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>119.94</t>
-        </is>
+      <c r="B33" t="n">
+        <v>119.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
         <v>38047</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>117.98</t>
-        </is>
+      <c r="B34" t="n">
+        <v>117.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
         <v>38139</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>123.65</t>
-        </is>
+      <c r="B35" t="n">
+        <v>123.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
         <v>38231</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>128.14</t>
-        </is>
+      <c r="B36" t="n">
+        <v>128.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
         <v>38322</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>127.39</t>
-        </is>
+      <c r="B37" t="n">
+        <v>127.39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
         <v>38412</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>122.92</t>
-        </is>
+      <c r="B38" t="n">
+        <v>122.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
         <v>38504</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>129.18</t>
-        </is>
+      <c r="B39" t="n">
+        <v>129.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
         <v>38596</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>130.85</t>
-        </is>
+      <c r="B40" t="n">
+        <v>130.85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
         <v>38687</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>130.13</t>
-        </is>
+      <c r="B41" t="n">
+        <v>130.13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
         <v>38777</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>128.18</t>
-        </is>
+      <c r="B42" t="n">
+        <v>128.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
         <v>38869</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>132.13</t>
-        </is>
+      <c r="B43" t="n">
+        <v>132.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
         <v>38961</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>136.72</t>
-        </is>
+      <c r="B44" t="n">
+        <v>136.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
         <v>39052</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>136.37</t>
-        </is>
+      <c r="B45" t="n">
+        <v>136.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
         <v>39142</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>134.84</t>
-        </is>
+      <c r="B46" t="n">
+        <v>134.84</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
         <v>39234</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>140.77</t>
-        </is>
+      <c r="B47" t="n">
+        <v>140.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
         <v>39326</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>144.75</t>
-        </is>
+      <c r="B48" t="n">
+        <v>144.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
         <v>39417</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>145.43</t>
-        </is>
+      <c r="B49" t="n">
+        <v>145.43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
         <v>39508</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>143.14</t>
-        </is>
+      <c r="B50" t="n">
+        <v>143.14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
         <v>39600</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>149.69</t>
-        </is>
+      <c r="B51" t="n">
+        <v>149.69</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
         <v>39692</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>154.86</t>
-        </is>
+      <c r="B52" t="n">
+        <v>154.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
         <v>39783</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>146.92</t>
-        </is>
+      <c r="B53" t="n">
+        <v>146.92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
         <v>39873</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>139.67</t>
-        </is>
+      <c r="B54" t="n">
+        <v>139.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>146.39</t>
-        </is>
+      <c r="B55" t="n">
+        <v>146.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
         <v>40057</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>153.06</t>
-        </is>
+      <c r="B56" t="n">
+        <v>153.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
         <v>40148</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>154.75</t>
-        </is>
+      <c r="B57" t="n">
+        <v>154.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
         <v>40238</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>152.53</t>
-        </is>
+      <c r="B58" t="n">
+        <v>152.53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
         <v>40330</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>158.86</t>
-        </is>
+      <c r="B59" t="n">
+        <v>158.86</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
         <v>40422</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>163.63</t>
-        </is>
+      <c r="B60" t="n">
+        <v>163.63</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
         <v>40513</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>163.55</t>
-        </is>
+      <c r="B61" t="n">
+        <v>163.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>40603</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>160.45</t>
-        </is>
+      <c r="B62" t="n">
+        <v>160.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
         <v>40695</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>166.33</t>
-        </is>
+      <c r="B63" t="n">
+        <v>166.33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
         <v>40787</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>169.41</t>
-        </is>
+      <c r="B64" t="n">
+        <v>169.41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
         <v>40878</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>167.75</t>
-        </is>
+      <c r="B65" t="n">
+        <v>167.75</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
         <v>40969</v>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>163.19</t>
-        </is>
+      <c r="B66" t="n">
+        <v>163.19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
         <v>41061</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>167.97</t>
-        </is>
+      <c r="B67" t="n">
+        <v>167.97</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
         <v>41153</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>173.63</t>
-        </is>
+      <c r="B68" t="n">
+        <v>173.63</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
         <v>41244</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>171.91</t>
-        </is>
+      <c r="B69" t="n">
+        <v>171.91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
         <v>41334</v>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>167.63</t>
-        </is>
+      <c r="B70" t="n">
+        <v>167.63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
         <v>41426</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>174.73</t>
-        </is>
+      <c r="B71" t="n">
+        <v>174.73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
         <v>41518</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>178.42</t>
-        </is>
+      <c r="B72" t="n">
+        <v>178.42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
         <v>41609</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>176.26</t>
-        </is>
+      <c r="B73" t="n">
+        <v>176.26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
         <v>41699</v>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>173.45</t>
-        </is>
+      <c r="B74" t="n">
+        <v>173.45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
         <v>41791</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>173.97</t>
-        </is>
+      <c r="B75" t="n">
+        <v>173.97</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
         <v>41883</v>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>177.28</t>
-        </is>
+      <c r="B76" t="n">
+        <v>177.28</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
         <v>41974</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>175.86</t>
-        </is>
+      <c r="B77" t="n">
+        <v>175.86</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
         <v>42064</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>170.64</t>
-        </is>
+      <c r="B78" t="n">
+        <v>170.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
         <v>42156</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>169.20</t>
-        </is>
+      <c r="B79" t="n">
+        <v>169.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
         <v>42248</v>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>169.72</t>
-        </is>
+      <c r="B80" t="n">
+        <v>169.72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
         <v>42339</v>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>166.15</t>
-        </is>
+      <c r="B81" t="n">
+        <v>166.15</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
         <v>42430</v>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>161.87</t>
-        </is>
+      <c r="B82" t="n">
+        <v>161.87</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
         <v>42522</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>163.75</t>
-        </is>
+      <c r="B83" t="n">
+        <v>163.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
         <v>42614</v>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>165.55</t>
-        </is>
+      <c r="B84" t="n">
+        <v>165.55</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
         <v>42705</v>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>162.39</t>
-        </is>
+      <c r="B85" t="n">
+        <v>162.39</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
         <v>42795</v>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>162.33</t>
-        </is>
+      <c r="B86" t="n">
+        <v>162.33</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
         <v>42887</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>165.04</t>
-        </is>
+      <c r="B87" t="n">
+        <v>165.04</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
         <v>42979</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>168.27</t>
-        </is>
+      <c r="B88" t="n">
+        <v>168.27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
         <v>43070</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>166.58</t>
-        </is>
+      <c r="B89" t="n">
+        <v>166.58</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
         <v>43160</v>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>165.42</t>
-        </is>
+      <c r="B90" t="n">
+        <v>165.42</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
         <v>43252</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>167.71</t>
-        </is>
+      <c r="B91" t="n">
+        <v>167.71</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
         <v>43344</v>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>171.73</t>
-        </is>
+      <c r="B92" t="n">
+        <v>171.73</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
         <v>43435</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>169.17</t>
-        </is>
+      <c r="B93" t="n">
+        <v>169.17</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
         <v>43525</v>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>166.91</t>
-        </is>
+      <c r="B94" t="n">
+        <v>166.91</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
         <v>43617</v>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>169.68</t>
-        </is>
+      <c r="B95" t="n">
+        <v>169.68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
         <v>43709</v>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>173.64</t>
-        </is>
+      <c r="B96" t="n">
+        <v>173.64</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
         <v>43800</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>172.03</t>
-        </is>
+      <c r="B97" t="n">
+        <v>172.03</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
         <v>43891</v>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>167.60</t>
-        </is>
+      <c r="B98" t="n">
+        <v>167.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
         <v>43983</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>152.48</t>
-        </is>
+      <c r="B99" t="n">
+        <v>152.48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
         <v>44075</v>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>168.37</t>
-        </is>
+      <c r="B100" t="n">
+        <v>168.37</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
         <v>44166</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>171.46</t>
-        </is>
+      <c r="B101" t="n">
+        <v>171.46</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
         <v>44256</v>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>170.53</t>
-        </is>
+      <c r="B102" t="n">
+        <v>170.53</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
         <v>44348</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>171.38</t>
-        </is>
+      <c r="B103" t="n">
+        <v>171.38</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
         <v>44440</v>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>175.46</t>
-        </is>
+      <c r="B104" t="n">
+        <v>175.46</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
         <v>44531</v>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>173.96</t>
-        </is>
+      <c r="B105" t="n">
+        <v>173.96</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
         <v>44621</v>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>173.05</t>
-        </is>
+      <c r="B106" t="n">
+        <v>173.05</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
         <v>44713</v>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>177.45</t>
-        </is>
+      <c r="B107" t="n">
+        <v>177.45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
         <v>44805</v>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>183.04</t>
-        </is>
+      <c r="B108" t="n">
+        <v>183.04</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>178.65</t>
-        </is>
+      <c r="B109" t="n">
+        <v>178.65</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
         <v>44986</v>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>180.74</t>
-        </is>
+      <c r="B110" t="n">
+        <v>180.74</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>184.28</t>
-        </is>
+      <c r="B111" t="n">
+        <v>184.28</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
         <v>45170</v>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>187.35</t>
-        </is>
+      <c r="B112" t="n">
+        <v>187.35</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
         <v>45261</v>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>182.90</t>
-        </is>
+      <c r="B113" t="n">
+        <v>182.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
         <v>45352</v>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>185.18</t>
-        </is>
+      <c r="B114" t="n">
+        <v>185.18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
         <v>45444</v>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>190.68</t>
-        </is>
+      <c r="B115" t="n">
+        <v>190.68</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
         <v>45536</v>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>195.10</t>
-        </is>
+      <c r="B116" t="n">
+        <v>195.1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
         <v>45627</v>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>189.45</t>
-        </is>
+      <c r="B117" t="n">
+        <v>189.45</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
         <v>45717</v>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>191.02</t>
-        </is>
+      <c r="B118" t="n">
+        <v>191.02</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
         <v>45809</v>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>195.18</t>
-        </is>
+      <c r="B119" t="n">
+        <v>195.18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
         <v>45901</v>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>198.66</t>
-        </is>
+      <c r="B120" t="n">
+        <v>198.66</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>192.94</t>
-        </is>
+      <c r="B121" t="n">
+        <v>192.94</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>194.53</t>
-        </is>
+      <c r="B122" t="n">
+        <v>194.53</v>
       </c>
     </row>
   </sheetData>
@@ -29423,7 +29181,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>cons_energ_indusrial</t>
+          <t>cons_energ_industrial</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -29672,10 +29430,8 @@
       <c r="AB4" t="n">
         <v>0.13</v>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>96.84</t>
-        </is>
+      <c r="AC4" t="n">
+        <v>96.84</v>
       </c>
     </row>
     <row r="5">
@@ -29823,10 +29579,8 @@
       <c r="AB7" t="n">
         <v>0.41</v>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>100.12</t>
-        </is>
+      <c r="AC7" t="n">
+        <v>100.12</v>
       </c>
     </row>
     <row r="8">
@@ -29974,10 +29728,8 @@
       <c r="AB10" t="n">
         <v>0.35</v>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>107.56</t>
-        </is>
+      <c r="AC10" t="n">
+        <v>107.56</v>
       </c>
     </row>
     <row r="11">
@@ -30125,10 +29877,8 @@
       <c r="AB13" t="n">
         <v>1.23</v>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>104.31</t>
-        </is>
+      <c r="AC13" t="n">
+        <v>104.31</v>
       </c>
     </row>
     <row r="14">
@@ -30276,10 +30026,8 @@
       <c r="AB16" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>100.13</t>
-        </is>
+      <c r="AC16" t="n">
+        <v>100.13</v>
       </c>
     </row>
     <row r="17">
@@ -30427,10 +30175,8 @@
       <c r="AB19" t="n">
         <v>0.32</v>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>104.88</t>
-        </is>
+      <c r="AC19" t="n">
+        <v>104.88</v>
       </c>
     </row>
     <row r="20">
@@ -30578,10 +30324,8 @@
       <c r="AB22" t="n">
         <v>0.73</v>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>109.49</t>
-        </is>
+      <c r="AC22" t="n">
+        <v>109.49</v>
       </c>
     </row>
     <row r="23">
@@ -30729,10 +30473,8 @@
       <c r="AB25" t="n">
         <v>0.97</v>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>108.21</t>
-        </is>
+      <c r="AC25" t="n">
+        <v>108.21</v>
       </c>
     </row>
     <row r="26">
@@ -30880,10 +30622,8 @@
       <c r="AB28" t="n">
         <v>0.12</v>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>101.14</t>
-        </is>
+      <c r="AC28" t="n">
+        <v>101.14</v>
       </c>
     </row>
     <row r="29">
@@ -31031,10 +30771,8 @@
       <c r="AB31" t="n">
         <v>0.38</v>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>106.46</t>
-        </is>
+      <c r="AC31" t="n">
+        <v>106.46</v>
       </c>
     </row>
     <row r="32">
@@ -31182,10 +30920,8 @@
       <c r="AB34" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>109.88</t>
-        </is>
+      <c r="AC34" t="n">
+        <v>109.88</v>
       </c>
     </row>
     <row r="35">
@@ -31333,10 +31069,8 @@
       <c r="AB37" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>106.66</t>
-        </is>
+      <c r="AC37" t="n">
+        <v>106.66</v>
       </c>
     </row>
     <row r="38">
@@ -31484,10 +31218,8 @@
       <c r="AB40" t="n">
         <v>4.16</v>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>101.92</t>
-        </is>
+      <c r="AC40" t="n">
+        <v>101.92</v>
       </c>
     </row>
     <row r="41">
@@ -31653,10 +31385,8 @@
       <c r="AB43" t="n">
         <v>0.33</v>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>106.04</t>
-        </is>
+      <c r="AC43" t="n">
+        <v>106.04</v>
       </c>
     </row>
     <row r="44">
@@ -31822,10 +31552,8 @@
       <c r="AB46" t="n">
         <v>2.16</v>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>109.20</t>
-        </is>
+      <c r="AC46" t="n">
+        <v>109.2</v>
       </c>
     </row>
     <row r="47">
@@ -31991,10 +31719,8 @@
       <c r="AB49" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>108.97</t>
-        </is>
+      <c r="AC49" t="n">
+        <v>108.97</v>
       </c>
     </row>
     <row r="50">
@@ -32160,10 +31886,8 @@
       <c r="AB52" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>106.40</t>
-        </is>
+      <c r="AC52" t="n">
+        <v>106.4</v>
       </c>
     </row>
     <row r="53">
@@ -32333,10 +32057,8 @@
       <c r="AB55" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>110.25</t>
-        </is>
+      <c r="AC55" t="n">
+        <v>110.25</v>
       </c>
     </row>
     <row r="56">
@@ -32508,10 +32230,8 @@
       <c r="AB58" t="n">
         <v>1.81</v>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>114.19</t>
-        </is>
+      <c r="AC58" t="n">
+        <v>114.19</v>
       </c>
     </row>
     <row r="59">
@@ -32683,10 +32403,8 @@
       <c r="AB61" t="n">
         <v>0.66</v>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>113.98</t>
-        </is>
+      <c r="AC61" t="n">
+        <v>113.98</v>
       </c>
     </row>
     <row r="62">
@@ -32858,10 +32576,8 @@
       <c r="AB64" t="n">
         <v>0.65</v>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>110.10</t>
-        </is>
+      <c r="AC64" t="n">
+        <v>110.1</v>
       </c>
     </row>
     <row r="65">
@@ -33033,10 +32749,8 @@
       <c r="AB67" t="n">
         <v>1.31</v>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>112.82</t>
-        </is>
+      <c r="AC67" t="n">
+        <v>112.82</v>
       </c>
     </row>
     <row r="68">
@@ -33208,10 +32922,8 @@
       <c r="AB70" t="n">
         <v>0.34</v>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>114.71</t>
-        </is>
+      <c r="AC70" t="n">
+        <v>114.71</v>
       </c>
     </row>
     <row r="71">
@@ -33383,10 +33095,8 @@
       <c r="AB73" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>113.38</t>
-        </is>
+      <c r="AC73" t="n">
+        <v>113.38</v>
       </c>
     </row>
     <row r="74">
@@ -33588,10 +33298,8 @@
       <c r="AB76" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>110.63</t>
-        </is>
+      <c r="AC76" t="n">
+        <v>110.63</v>
       </c>
     </row>
     <row r="77">
@@ -33793,10 +33501,8 @@
       <c r="AB79" t="n">
         <v>2.31</v>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>115.41</t>
-        </is>
+      <c r="AC79" t="n">
+        <v>115.41</v>
       </c>
     </row>
     <row r="80">
@@ -33998,10 +33704,8 @@
       <c r="AB82" t="n">
         <v>3.43</v>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>119.50</t>
-        </is>
+      <c r="AC82" t="n">
+        <v>119.5</v>
       </c>
     </row>
     <row r="83">
@@ -34203,10 +33907,8 @@
       <c r="AB85" t="n">
         <v>4.45</v>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>119.24</t>
-        </is>
+      <c r="AC85" t="n">
+        <v>119.24</v>
       </c>
     </row>
     <row r="86">
@@ -34432,10 +34134,8 @@
       <c r="AB88" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>113.58</t>
-        </is>
+      <c r="AC88" t="n">
+        <v>113.58</v>
       </c>
     </row>
     <row r="89">
@@ -34661,10 +34361,8 @@
       <c r="AB91" t="n">
         <v>-1.67</v>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>116.31</t>
-        </is>
+      <c r="AC91" t="n">
+        <v>116.31</v>
       </c>
     </row>
     <row r="92">
@@ -34890,10 +34588,8 @@
       <c r="AB94" t="n">
         <v>1.54</v>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>120.25</t>
-        </is>
+      <c r="AC94" t="n">
+        <v>120.25</v>
       </c>
     </row>
     <row r="95">
@@ -35119,10 +34815,8 @@
       <c r="AB97" t="n">
         <v>0.64</v>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>119.94</t>
-        </is>
+      <c r="AC97" t="n">
+        <v>119.94</v>
       </c>
     </row>
     <row r="98">
@@ -35348,10 +35042,8 @@
       <c r="AB100" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>117.98</t>
-        </is>
+      <c r="AC100" t="n">
+        <v>117.98</v>
       </c>
     </row>
     <row r="101">
@@ -35577,10 +35269,8 @@
       <c r="AB103" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>123.65</t>
-        </is>
+      <c r="AC103" t="n">
+        <v>123.65</v>
       </c>
     </row>
     <row r="104">
@@ -35806,10 +35496,8 @@
       <c r="AB106" t="n">
         <v>0.9</v>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>128.14</t>
-        </is>
+      <c r="AC106" t="n">
+        <v>128.14</v>
       </c>
     </row>
     <row r="107">
@@ -36035,10 +35723,8 @@
       <c r="AB109" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>127.39</t>
-        </is>
+      <c r="AC109" t="n">
+        <v>127.39</v>
       </c>
     </row>
     <row r="110">
@@ -36264,10 +35950,8 @@
       <c r="AB112" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>122.92</t>
-        </is>
+      <c r="AC112" t="n">
+        <v>122.92</v>
       </c>
     </row>
     <row r="113">
@@ -36493,10 +36177,8 @@
       <c r="AB115" t="n">
         <v>-1</v>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>129.18</t>
-        </is>
+      <c r="AC115" t="n">
+        <v>129.18</v>
       </c>
     </row>
     <row r="116">
@@ -36722,10 +36404,8 @@
       <c r="AB118" t="n">
         <v>-0.76</v>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>130.85</t>
-        </is>
+      <c r="AC118" t="n">
+        <v>130.85</v>
       </c>
     </row>
     <row r="119">
@@ -36951,10 +36631,8 @@
       <c r="AB121" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>130.13</t>
-        </is>
+      <c r="AC121" t="n">
+        <v>130.13</v>
       </c>
     </row>
     <row r="122">
@@ -37180,10 +36858,8 @@
       <c r="AB124" t="n">
         <v>-0.48</v>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>128.18</t>
-        </is>
+      <c r="AC124" t="n">
+        <v>128.18</v>
       </c>
     </row>
     <row r="125">
@@ -37409,10 +37085,8 @@
       <c r="AB127" t="n">
         <v>1.11</v>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>132.13</t>
-        </is>
+      <c r="AC127" t="n">
+        <v>132.13</v>
       </c>
     </row>
     <row r="128">
@@ -37638,10 +37312,8 @@
       <c r="AB130" t="n">
         <v>0.36</v>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>136.72</t>
-        </is>
+      <c r="AC130" t="n">
+        <v>136.72</v>
       </c>
     </row>
     <row r="131">
@@ -37867,10 +37539,8 @@
       <c r="AB133" t="n">
         <v>0.29</v>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>136.37</t>
-        </is>
+      <c r="AC133" t="n">
+        <v>136.37</v>
       </c>
     </row>
     <row r="134">
@@ -38096,10 +37766,8 @@
       <c r="AB136" t="n">
         <v>0.33</v>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>134.84</t>
-        </is>
+      <c r="AC136" t="n">
+        <v>134.84</v>
       </c>
     </row>
     <row r="137">
@@ -38325,10 +37993,8 @@
       <c r="AB139" t="n">
         <v>0.01</v>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>140.77</t>
-        </is>
+      <c r="AC139" t="n">
+        <v>140.77</v>
       </c>
     </row>
     <row r="140">
@@ -38554,10 +38220,8 @@
       <c r="AB142" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>144.75</t>
-        </is>
+      <c r="AC142" t="n">
+        <v>144.75</v>
       </c>
     </row>
     <row r="143">
@@ -38783,10 +38447,8 @@
       <c r="AB145" t="n">
         <v>2.36</v>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>145.43</t>
-        </is>
+      <c r="AC145" t="n">
+        <v>145.43</v>
       </c>
     </row>
     <row r="146">
@@ -39012,10 +38674,8 @@
       <c r="AB148" t="n">
         <v>0.96</v>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>143.14</t>
-        </is>
+      <c r="AC148" t="n">
+        <v>143.14</v>
       </c>
     </row>
     <row r="149">
@@ -39247,10 +38907,8 @@
       <c r="AB151" t="n">
         <v>2.27</v>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>149.69</t>
-        </is>
+      <c r="AC151" t="n">
+        <v>149.69</v>
       </c>
     </row>
     <row r="152">
@@ -39494,10 +39152,8 @@
       <c r="AB154" t="n">
         <v>0.04</v>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>154.86</t>
-        </is>
+      <c r="AC154" t="n">
+        <v>154.86</v>
       </c>
     </row>
     <row r="155">
@@ -39741,10 +39397,8 @@
       <c r="AB157" t="n">
         <v>-0.42</v>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>146.92</t>
-        </is>
+      <c r="AC157" t="n">
+        <v>146.92</v>
       </c>
     </row>
     <row r="158">
@@ -39988,10 +39642,8 @@
       <c r="AB160" t="n">
         <v>-1.24</v>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>139.67</t>
-        </is>
+      <c r="AC160" t="n">
+        <v>139.67</v>
       </c>
     </row>
     <row r="161">
@@ -40235,10 +39887,8 @@
       <c r="AB163" t="n">
         <v>-0.45</v>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>146.39</t>
-        </is>
+      <c r="AC163" t="n">
+        <v>146.39</v>
       </c>
     </row>
     <row r="164">
@@ -40482,10 +40132,8 @@
       <c r="AB166" t="n">
         <v>0.53</v>
       </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>153.06</t>
-        </is>
+      <c r="AC166" t="n">
+        <v>153.06</v>
       </c>
     </row>
     <row r="167">
@@ -40729,10 +40377,8 @@
       <c r="AB169" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>154.75</t>
-        </is>
+      <c r="AC169" t="n">
+        <v>154.75</v>
       </c>
     </row>
     <row r="170">
@@ -40976,10 +40622,8 @@
       <c r="AB172" t="n">
         <v>1.07</v>
       </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>152.53</t>
-        </is>
+      <c r="AC172" t="n">
+        <v>152.53</v>
       </c>
     </row>
     <row r="173">
@@ -41223,10 +40867,8 @@
       <c r="AB175" t="n">
         <v>1.09</v>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>158.86</t>
-        </is>
+      <c r="AC175" t="n">
+        <v>158.86</v>
       </c>
     </row>
     <row r="176">
@@ -41470,10 +41112,8 @@
       <c r="AB178" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>163.63</t>
-        </is>
+      <c r="AC178" t="n">
+        <v>163.63</v>
       </c>
     </row>
     <row r="179">
@@ -41717,10 +41357,8 @@
       <c r="AB181" t="n">
         <v>0.63</v>
       </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>163.55</t>
-        </is>
+      <c r="AC181" t="n">
+        <v>163.55</v>
       </c>
     </row>
     <row r="182">
@@ -41964,10 +41602,8 @@
       <c r="AB184" t="n">
         <v>0.65</v>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>160.45</t>
-        </is>
+      <c r="AC184" t="n">
+        <v>160.45</v>
       </c>
     </row>
     <row r="185">
@@ -42211,10 +41847,8 @@
       <c r="AB187" t="n">
         <v>-0.45</v>
       </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>166.33</t>
-        </is>
+      <c r="AC187" t="n">
+        <v>166.33</v>
       </c>
     </row>
     <row r="188">
@@ -42458,10 +42092,8 @@
       <c r="AB190" t="n">
         <v>0.74</v>
       </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>169.41</t>
-        </is>
+      <c r="AC190" t="n">
+        <v>169.41</v>
       </c>
     </row>
     <row r="191">
@@ -42705,10 +42337,8 @@
       <c r="AB193" t="n">
         <v>-0.48</v>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>167.75</t>
-        </is>
+      <c r="AC193" t="n">
+        <v>167.75</v>
       </c>
     </row>
     <row r="194">
@@ -42962,10 +42592,8 @@
       <c r="AB196" t="n">
         <v>0.42</v>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>163.19</t>
-        </is>
+      <c r="AC196" t="n">
+        <v>163.19</v>
       </c>
     </row>
     <row r="197">
@@ -43227,10 +42855,8 @@
       <c r="AB199" t="n">
         <v>0.74</v>
       </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>167.97</t>
-        </is>
+      <c r="AC199" t="n">
+        <v>167.97</v>
       </c>
     </row>
     <row r="200">
@@ -43492,10 +43118,8 @@
       <c r="AB202" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>173.63</t>
-        </is>
+      <c r="AC202" t="n">
+        <v>173.63</v>
       </c>
     </row>
     <row r="203">
@@ -43757,10 +43381,8 @@
       <c r="AB205" t="n">
         <v>0.73</v>
       </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>171.91</t>
-        </is>
+      <c r="AC205" t="n">
+        <v>171.91</v>
       </c>
     </row>
     <row r="206">
@@ -44022,10 +43644,8 @@
       <c r="AB208" t="n">
         <v>0.01</v>
       </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>167.63</t>
-        </is>
+      <c r="AC208" t="n">
+        <v>167.63</v>
       </c>
     </row>
     <row r="209">
@@ -44287,10 +43907,8 @@
       <c r="AB211" t="n">
         <v>0.68</v>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>174.73</t>
-        </is>
+      <c r="AC211" t="n">
+        <v>174.73</v>
       </c>
     </row>
     <row r="212">
@@ -44552,10 +44170,8 @@
       <c r="AB214" t="n">
         <v>2.11</v>
       </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>178.42</t>
-        </is>
+      <c r="AC214" t="n">
+        <v>178.42</v>
       </c>
     </row>
     <row r="215">
@@ -44817,10 +44433,8 @@
       <c r="AB217" t="n">
         <v>0.63</v>
       </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>176.26</t>
-        </is>
+      <c r="AC217" t="n">
+        <v>176.26</v>
       </c>
     </row>
     <row r="218">
@@ -45082,10 +44696,8 @@
       <c r="AB220" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>173.45</t>
-        </is>
+      <c r="AC220" t="n">
+        <v>173.45</v>
       </c>
     </row>
     <row r="221">
@@ -45347,10 +44959,8 @@
       <c r="AB223" t="n">
         <v>-1.44</v>
       </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>173.97</t>
-        </is>
+      <c r="AC223" t="n">
+        <v>173.97</v>
       </c>
     </row>
     <row r="224">
@@ -45612,10 +45222,8 @@
       <c r="AB226" t="n">
         <v>0.13</v>
       </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>177.28</t>
-        </is>
+      <c r="AC226" t="n">
+        <v>177.28</v>
       </c>
     </row>
     <row r="227">
@@ -45877,10 +45485,8 @@
       <c r="AB229" t="n">
         <v>0.63</v>
       </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>175.86</t>
-        </is>
+      <c r="AC229" t="n">
+        <v>175.86</v>
       </c>
     </row>
     <row r="230">
@@ -46142,10 +45748,8 @@
       <c r="AB232" t="n">
         <v>0.92</v>
       </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>170.64</t>
-        </is>
+      <c r="AC232" t="n">
+        <v>170.64</v>
       </c>
     </row>
     <row r="233">
@@ -46407,10 +46011,8 @@
       <c r="AB235" t="n">
         <v>0.41</v>
       </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>169.20</t>
-        </is>
+      <c r="AC235" t="n">
+        <v>169.2</v>
       </c>
     </row>
     <row r="236">
@@ -46672,10 +46274,8 @@
       <c r="AB238" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>169.72</t>
-        </is>
+      <c r="AC238" t="n">
+        <v>169.72</v>
       </c>
     </row>
     <row r="239">
@@ -46937,10 +46537,8 @@
       <c r="AB241" t="n">
         <v>0.39</v>
       </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>166.15</t>
-        </is>
+      <c r="AC241" t="n">
+        <v>166.15</v>
       </c>
     </row>
     <row r="242">
@@ -47202,10 +46800,8 @@
       <c r="AB244" t="n">
         <v>0.44</v>
       </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>161.87</t>
-        </is>
+      <c r="AC244" t="n">
+        <v>161.87</v>
       </c>
     </row>
     <row r="245">
@@ -47467,10 +47063,8 @@
       <c r="AB247" t="n">
         <v>2.21</v>
       </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>163.75</t>
-        </is>
+      <c r="AC247" t="n">
+        <v>163.75</v>
       </c>
     </row>
     <row r="248">
@@ -47732,10 +47326,8 @@
       <c r="AB250" t="n">
         <v>0.18</v>
       </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>165.55</t>
-        </is>
+      <c r="AC250" t="n">
+        <v>165.55</v>
       </c>
     </row>
     <row r="251">
@@ -47997,10 +47589,8 @@
       <c r="AB253" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>162.39</t>
-        </is>
+      <c r="AC253" t="n">
+        <v>162.39</v>
       </c>
     </row>
     <row r="254">
@@ -48262,10 +47852,8 @@
       <c r="AB256" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>162.33</t>
-        </is>
+      <c r="AC256" t="n">
+        <v>162.33</v>
       </c>
     </row>
     <row r="257">
@@ -48527,10 +48115,8 @@
       <c r="AB259" t="n">
         <v>-1.22</v>
       </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>165.04</t>
-        </is>
+      <c r="AC259" t="n">
+        <v>165.04</v>
       </c>
     </row>
     <row r="260">
@@ -48792,10 +48378,8 @@
       <c r="AB262" t="n">
         <v>0.74</v>
       </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>168.27</t>
-        </is>
+      <c r="AC262" t="n">
+        <v>168.27</v>
       </c>
     </row>
     <row r="263">
@@ -49057,10 +48641,8 @@
       <c r="AB265" t="n">
         <v>1.24</v>
       </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>166.58</t>
-        </is>
+      <c r="AC265" t="n">
+        <v>166.58</v>
       </c>
     </row>
     <row r="266">
@@ -49322,10 +48904,8 @@
       <c r="AB268" t="n">
         <v>0.89</v>
       </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>165.42</t>
-        </is>
+      <c r="AC268" t="n">
+        <v>165.42</v>
       </c>
     </row>
     <row r="269">
@@ -49587,10 +49167,8 @@
       <c r="AB271" t="n">
         <v>2.33</v>
       </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>167.71</t>
-        </is>
+      <c r="AC271" t="n">
+        <v>167.71</v>
       </c>
     </row>
     <row r="272">
@@ -49852,10 +49430,8 @@
       <c r="AB274" t="n">
         <v>2.19</v>
       </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>171.73</t>
-        </is>
+      <c r="AC274" t="n">
+        <v>171.73</v>
       </c>
     </row>
     <row r="275">
@@ -50117,10 +49693,8 @@
       <c r="AB277" t="n">
         <v>-1.67</v>
       </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>169.17</t>
-        </is>
+      <c r="AC277" t="n">
+        <v>169.17</v>
       </c>
     </row>
     <row r="278">
@@ -50382,10 +49956,8 @@
       <c r="AB280" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>166.91</t>
-        </is>
+      <c r="AC280" t="n">
+        <v>166.91</v>
       </c>
     </row>
     <row r="281">
@@ -50647,10 +50219,8 @@
       <c r="AB283" t="n">
         <v>1.16</v>
       </c>
-      <c r="AC283" t="inlineStr">
-        <is>
-          <t>169.68</t>
-        </is>
+      <c r="AC283" t="n">
+        <v>169.68</v>
       </c>
     </row>
     <row r="284">
@@ -50912,10 +50482,8 @@
       <c r="AB286" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AC286" t="inlineStr">
-        <is>
-          <t>173.64</t>
-        </is>
+      <c r="AC286" t="n">
+        <v>173.64</v>
       </c>
     </row>
     <row r="287">
@@ -51177,10 +50745,8 @@
       <c r="AB289" t="n">
         <v>2.84</v>
       </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>172.03</t>
-        </is>
+      <c r="AC289" t="n">
+        <v>172.03</v>
       </c>
     </row>
     <row r="290">
@@ -51442,10 +51008,8 @@
       <c r="AB292" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC292" t="inlineStr">
-        <is>
-          <t>167.60</t>
-        </is>
+      <c r="AC292" t="n">
+        <v>167.6</v>
       </c>
     </row>
     <row r="293">
@@ -51707,10 +51271,8 @@
       <c r="AB295" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC295" t="inlineStr">
-        <is>
-          <t>152.48</t>
-        </is>
+      <c r="AC295" t="n">
+        <v>152.48</v>
       </c>
     </row>
     <row r="296">
@@ -51972,10 +51534,8 @@
       <c r="AB298" t="n">
         <v>5.92</v>
       </c>
-      <c r="AC298" t="inlineStr">
-        <is>
-          <t>168.37</t>
-        </is>
+      <c r="AC298" t="n">
+        <v>168.37</v>
       </c>
     </row>
     <row r="299">
@@ -52237,10 +51797,8 @@
       <c r="AB301" t="n">
         <v>0.9</v>
       </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>171.46</t>
-        </is>
+      <c r="AC301" t="n">
+        <v>171.46</v>
       </c>
     </row>
     <row r="302">
@@ -52502,10 +52060,8 @@
       <c r="AB304" t="n">
         <v>3.56</v>
       </c>
-      <c r="AC304" t="inlineStr">
-        <is>
-          <t>170.53</t>
-        </is>
+      <c r="AC304" t="n">
+        <v>170.53</v>
       </c>
     </row>
     <row r="305">
@@ -52767,10 +52323,8 @@
       <c r="AB307" t="n">
         <v>0.42</v>
       </c>
-      <c r="AC307" t="inlineStr">
-        <is>
-          <t>171.38</t>
-        </is>
+      <c r="AC307" t="n">
+        <v>171.38</v>
       </c>
     </row>
     <row r="308">
@@ -53032,10 +52586,8 @@
       <c r="AB310" t="n">
         <v>-1.21</v>
       </c>
-      <c r="AC310" t="inlineStr">
-        <is>
-          <t>175.46</t>
-        </is>
+      <c r="AC310" t="n">
+        <v>175.46</v>
       </c>
     </row>
     <row r="311">
@@ -53297,10 +52849,8 @@
       <c r="AB313" t="n">
         <v>0.95</v>
       </c>
-      <c r="AC313" t="inlineStr">
-        <is>
-          <t>173.96</t>
-        </is>
+      <c r="AC313" t="n">
+        <v>173.96</v>
       </c>
     </row>
     <row r="314">
@@ -53562,10 +53112,8 @@
       <c r="AB316" t="n">
         <v>2.07</v>
       </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>173.05</t>
-        </is>
+      <c r="AC316" t="n">
+        <v>173.05</v>
       </c>
     </row>
     <row r="317">
@@ -53827,10 +53375,8 @@
       <c r="AB319" t="n">
         <v>0.3</v>
       </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>177.45</t>
-        </is>
+      <c r="AC319" t="n">
+        <v>177.45</v>
       </c>
     </row>
     <row r="320">
@@ -54092,10 +53638,8 @@
       <c r="AB322" t="n">
         <v>-1.27</v>
       </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>183.04</t>
-        </is>
+      <c r="AC322" t="n">
+        <v>183.04</v>
       </c>
     </row>
     <row r="323">
@@ -54357,10 +53901,8 @@
       <c r="AB325" t="n">
         <v>0.47</v>
       </c>
-      <c r="AC325" t="inlineStr">
-        <is>
-          <t>178.65</t>
-        </is>
+      <c r="AC325" t="n">
+        <v>178.65</v>
       </c>
     </row>
     <row r="326">
@@ -54622,10 +54164,8 @@
       <c r="AB328" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AC328" t="inlineStr">
-        <is>
-          <t>180.74</t>
-        </is>
+      <c r="AC328" t="n">
+        <v>180.74</v>
       </c>
     </row>
     <row r="329">
@@ -54887,10 +54427,8 @@
       <c r="AB331" t="n">
         <v>-2.73</v>
       </c>
-      <c r="AC331" t="inlineStr">
-        <is>
-          <t>184.28</t>
-        </is>
+      <c r="AC331" t="n">
+        <v>184.28</v>
       </c>
     </row>
     <row r="332">
@@ -55152,10 +54690,8 @@
       <c r="AB334" t="n">
         <v>0.41</v>
       </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>187.35</t>
-        </is>
+      <c r="AC334" t="n">
+        <v>187.35</v>
       </c>
     </row>
     <row r="335">
@@ -55417,10 +54953,8 @@
       <c r="AB337" t="n">
         <v>0.97</v>
       </c>
-      <c r="AC337" t="inlineStr">
-        <is>
-          <t>182.90</t>
-        </is>
+      <c r="AC337" t="n">
+        <v>182.9</v>
       </c>
     </row>
     <row r="338">
@@ -55682,10 +55216,8 @@
       <c r="AB340" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AC340" t="inlineStr">
-        <is>
-          <t>185.18</t>
-        </is>
+      <c r="AC340" t="n">
+        <v>185.18</v>
       </c>
     </row>
     <row r="341">
@@ -55947,10 +55479,8 @@
       <c r="AB343" t="n">
         <v>0.89</v>
       </c>
-      <c r="AC343" t="inlineStr">
-        <is>
-          <t>190.68</t>
-        </is>
+      <c r="AC343" t="n">
+        <v>190.68</v>
       </c>
     </row>
     <row r="344">
@@ -56212,10 +55742,8 @@
       <c r="AB346" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC346" t="inlineStr">
-        <is>
-          <t>195.10</t>
-        </is>
+      <c r="AC346" t="n">
+        <v>195.1</v>
       </c>
     </row>
     <row r="347">
@@ -56477,10 +56005,8 @@
       <c r="AB349" t="n">
         <v>1.21</v>
       </c>
-      <c r="AC349" t="inlineStr">
-        <is>
-          <t>189.45</t>
-        </is>
+      <c r="AC349" t="n">
+        <v>189.45</v>
       </c>
     </row>
     <row r="350">
@@ -56742,10 +56268,8 @@
       <c r="AB352" t="n">
         <v>-0.73</v>
       </c>
-      <c r="AC352" t="inlineStr">
-        <is>
-          <t>191.02</t>
-        </is>
+      <c r="AC352" t="n">
+        <v>191.02</v>
       </c>
     </row>
     <row r="353">
@@ -57007,10 +56531,8 @@
       <c r="AB355" t="n">
         <v>-2.53</v>
       </c>
-      <c r="AC355" t="inlineStr">
-        <is>
-          <t>195.18</t>
-        </is>
+      <c r="AC355" t="n">
+        <v>195.18</v>
       </c>
     </row>
     <row r="356">
@@ -57272,10 +56794,8 @@
       <c r="AB358" t="n">
         <v>0.49</v>
       </c>
-      <c r="AC358" t="inlineStr">
-        <is>
-          <t>198.66</t>
-        </is>
+      <c r="AC358" t="n">
+        <v>198.66</v>
       </c>
     </row>
     <row r="359">
@@ -57537,10 +57057,8 @@
       <c r="AB361" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AC361" t="inlineStr">
-        <is>
-          <t>192.94</t>
-        </is>
+      <c r="AC361" t="n">
+        <v>192.94</v>
       </c>
     </row>
     <row r="362">
@@ -57802,10 +57320,8 @@
       <c r="AB364" t="n">
         <v>0.61</v>
       </c>
-      <c r="AC364" t="inlineStr">
-        <is>
-          <t>194.53</t>
-        </is>
+      <c r="AC364" t="n">
+        <v>194.53</v>
       </c>
     </row>
     <row r="365">
